--- a/data/gold/results/scenarios/health_only/table_s5_dk.xlsx
+++ b/data/gold/results/scenarios/health_only/table_s5_dk.xlsx
@@ -388,13 +388,13 @@
         <v>3</v>
       </c>
       <c r="B2">
-        <v>4405.157648990035</v>
+        <v>4119.043228087125</v>
       </c>
       <c r="C2">
-        <v>64720.67119886602</v>
+        <v>77477.50333386465</v>
       </c>
       <c r="D2">
-        <v>6.806415272570936</v>
+        <v>5.316437741078747</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -402,13 +402,13 @@
         <v>4</v>
       </c>
       <c r="B3">
-        <v>5123.295820701995</v>
+        <v>3684.859392415446</v>
       </c>
       <c r="C3">
-        <v>81896.03408341862</v>
+        <v>53939.28050941755</v>
       </c>
       <c r="D3">
-        <v>6.255853385383043</v>
+        <v>6.831495262106967</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -416,13 +416,13 @@
         <v>5</v>
       </c>
       <c r="B4">
-        <v>38.90477499646222</v>
+        <v>84.42245303168855</v>
       </c>
       <c r="C4">
-        <v>883.0636615745001</v>
+        <v>1276.414575312263</v>
       </c>
       <c r="D4">
-        <v>4.405659148865339</v>
+        <v>6.614030790978346</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -430,13 +430,13 @@
         <v>6</v>
       </c>
       <c r="B5">
-        <v>3414.079538858508</v>
+        <v>4097.430362241296</v>
       </c>
       <c r="C5">
-        <v>86351.7602835304</v>
+        <v>99466.18032506436</v>
       </c>
       <c r="D5">
-        <v>3.953688410807839</v>
+        <v>4.119420640111572</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -444,13 +444,13 @@
         <v>7</v>
       </c>
       <c r="B6">
-        <v>1353.678251672859</v>
+        <v>228.9332290733108</v>
       </c>
       <c r="C6">
-        <v>23660.11065987919</v>
+        <v>10587.34124489906</v>
       </c>
       <c r="D6">
-        <v>5.721352157360413</v>
+        <v>2.162329746229819</v>
       </c>
     </row>
   </sheetData>

--- a/data/gold/results/scenarios/health_only/table_s5_dk.xlsx
+++ b/data/gold/results/scenarios/health_only/table_s5_dk.xlsx
@@ -402,13 +402,13 @@
         <v>4</v>
       </c>
       <c r="B3">
-        <v>3684.859392415446</v>
+        <v>3682.962592415446</v>
       </c>
       <c r="C3">
         <v>53939.28050941755</v>
       </c>
       <c r="D3">
-        <v>6.831495262106967</v>
+        <v>6.827978715386124</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -416,13 +416,13 @@
         <v>5</v>
       </c>
       <c r="B4">
-        <v>84.42245303168855</v>
+        <v>84.40895303168854</v>
       </c>
       <c r="C4">
         <v>1276.414575312263</v>
       </c>
       <c r="D4">
-        <v>6.614030790978346</v>
+        <v>6.612973140880869</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -430,13 +430,13 @@
         <v>6</v>
       </c>
       <c r="B5">
-        <v>4097.430362241296</v>
+        <v>4097.307162241296</v>
       </c>
       <c r="C5">
         <v>99466.18032506436</v>
       </c>
       <c r="D5">
-        <v>4.119420640111572</v>
+        <v>4.119296778916141</v>
       </c>
     </row>
     <row r="6" spans="1:4">
